--- a/resources/excel_templates/gb_t_32151_34_2024_appendix_b_v9.xlsx
+++ b/resources/excel_templates/gb_t_32151_34_2024_appendix_b_v9.xlsx
@@ -4271,7 +4271,7 @@
     <row r="8" ht="72" customHeight="1" s="42">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>数据提示：烟气分段输入规则 V9（2.7.0）。每行对应真实源实例/同计量边界的一个监测段；同实例同边界复用同编号，不同真实实例用不同编号；段编号唯一。K/L以文字填写真实起止时间（年-月-日 时:分:秒，终点不含），M选d或h，F为本段时长且与区间精确一致。Q与QVar及参数只属于本段。报告期独立，不回填段时长；缺口只形成已覆盖合计，不补零、不年化。结果列G不填写，新增行位于本提示上方。</t>
+          <t>数据提示：烟气分段输入规则 V9（2.7.0）。每行对应真实源实例/同计量边界的一个监测段；同实例同边界复用同编号，不同真实实例用不同编号；段编号唯一。K/L以文字填写真实起止时间（年-月-日 时:00，须为整小时，分钟/秒为0，终点不含，不自动截断），M优先选h并在F填整数小时；d按软件小时转天规范化值全值校验，不用显示近似值。Q与QVar及参数只属于本段。报告期独立，不回填段时长；缺口只形成已覆盖合计，不补零、不年化。结果列G不填写，新增行位于本提示上方。</t>
         </is>
       </c>
     </row>
